--- a/assets/spreadsheets/Hotel_vs_MF_Cap_Rate_Spread_Analysis.xlsx
+++ b/assets/spreadsheets/Hotel_vs_MF_Cap_Rate_Spread_Analysis.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10913"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangziyao/Desktop/HotelShift-Project2/assets/spreadsheets/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530EEE3E-1940-904A-9E72-32185EF41854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="760" windowWidth="24240" windowHeight="18000" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="20240" windowHeight="13560" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Class C Apartment Cap Rates" sheetId="4" r:id="rId1"/>
@@ -18,43 +12,8 @@
     <sheet name="Cap Rate Spread Analysis" sheetId="2" r:id="rId3"/>
     <sheet name="Regulatory Environment" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1341,6 +1300,12 @@
     <t>Rank</t>
   </si>
   <si>
+    <t>Hotel Cap Rate</t>
+  </si>
+  <si>
+    <t>MF Cap Rate</t>
+  </si>
+  <si>
     <t>SPREAD (bps)</t>
   </si>
   <si>
@@ -1774,25 +1739,23 @@
   </si>
   <si>
     <t>[A] VERY FAVORABLE — No rent control. Minimal tenant protections. Fast eviction. Very low regulatory burden. But extremely small market.</t>
-  </si>
-  <si>
-    <t>Hotel Cap Rate</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>MF Cap Rate</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1800,122 +1763,259 @@
       <b/>
       <sz val="13"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF996633"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1976,8 +2076,170 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1994,12 +2256,256 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2056,6 +2562,8 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2074,6 +2582,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2086,24 +2595,62 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2388,14 +2935,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2405,2183 +2952,2129 @@
     <col min="6" max="6" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19">
+    <row r="1" ht="20.4" spans="1:1">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-    </row>
-    <row r="2" spans="1:6" ht="15">
-      <c r="A2" s="33" t="s">
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-    </row>
-    <row r="4" spans="1:6" ht="16">
-      <c r="A4" s="27" t="s">
+    </row>
+    <row r="4" ht="17" spans="1:6">
+      <c r="A4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="32" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="45">
-      <c r="A5" s="28" t="s">
+    <row r="5" ht="34" spans="1:6">
+      <c r="A5" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="33" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="45">
-      <c r="A6" s="4" t="s">
+    <row r="6" ht="51" spans="1:6">
+      <c r="A6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="45">
-      <c r="A7" s="28" t="s">
+    <row r="7" ht="51" spans="1:6">
+      <c r="A7" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="33" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="45">
-      <c r="A8" s="4" t="s">
+    <row r="8" ht="34" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="45">
-      <c r="A9" s="28" t="s">
+    <row r="9" ht="51" spans="1:6">
+      <c r="A9" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="33" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="45">
-      <c r="A10" s="4" t="s">
+    <row r="10" ht="51" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="45">
-      <c r="A11" s="28" t="s">
+    <row r="11" ht="34" spans="1:6">
+      <c r="A11" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="33" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="45">
-      <c r="A12" s="4" t="s">
+    <row r="12" ht="51" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="45">
-      <c r="A13" s="28" t="s">
+    <row r="13" ht="51" spans="1:6">
+      <c r="A13" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="33" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="45">
-      <c r="A14" s="4" t="s">
+    <row r="14" ht="51" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="45">
-      <c r="A15" s="28" t="s">
+    <row r="15" ht="51" spans="1:6">
+      <c r="A15" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="33" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="45">
-      <c r="A16" s="4" t="s">
+    <row r="16" ht="34" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="45">
-      <c r="A17" s="28" t="s">
+    <row r="17" ht="51" spans="1:6">
+      <c r="A17" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="28" t="s">
+      <c r="F17" s="33" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="45">
-      <c r="A18" s="4" t="s">
+    <row r="18" ht="51" spans="1:6">
+      <c r="A18" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="45">
-      <c r="A19" s="28" t="s">
+    <row r="19" ht="34" spans="1:6">
+      <c r="A19" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="F19" s="33" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="45">
-      <c r="A20" s="4" t="s">
+    <row r="20" ht="34" spans="1:6">
+      <c r="A20" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="45">
-      <c r="A21" s="28" t="s">
+    <row r="21" ht="34" spans="1:6">
+      <c r="A21" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="F21" s="33" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="45">
-      <c r="A22" s="4" t="s">
+    <row r="22" ht="51" spans="1:6">
+      <c r="A22" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="45">
-      <c r="A23" s="28" t="s">
+    <row r="23" ht="34" spans="1:6">
+      <c r="A23" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="F23" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="45">
-      <c r="A24" s="4" t="s">
+    <row r="24" ht="34" spans="1:6">
+      <c r="A24" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="45">
-      <c r="A25" s="28" t="s">
+    <row r="25" ht="51" spans="1:6">
+      <c r="A25" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="E25" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="F25" s="28" t="s">
+      <c r="F25" s="33" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="45">
-      <c r="A26" s="4" t="s">
+    <row r="26" ht="34" spans="1:6">
+      <c r="A26" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="45">
-      <c r="A27" s="28" t="s">
+    <row r="27" ht="34" spans="1:6">
+      <c r="A27" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="E27" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="F27" s="33" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="45">
-      <c r="A28" s="4" t="s">
+    <row r="28" ht="51" spans="1:6">
+      <c r="A28" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B28" s="30" t="s">
+      <c r="B28" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="45">
-      <c r="A29" s="28" t="s">
+    <row r="29" ht="34" spans="1:6">
+      <c r="A29" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="D29" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="E29" s="28" t="s">
+      <c r="E29" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="33" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="45">
-      <c r="A30" s="4" t="s">
+    <row r="30" ht="34" spans="1:6">
+      <c r="A30" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="45">
-      <c r="A31" s="28" t="s">
+    <row r="31" ht="34" spans="1:6">
+      <c r="A31" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="E31" s="28" t="s">
+      <c r="E31" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="F31" s="28" t="s">
+      <c r="F31" s="33" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="45">
-      <c r="A32" s="4" t="s">
+    <row r="32" ht="34" spans="1:6">
+      <c r="A32" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="6" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="45">
-      <c r="A33" s="28" t="s">
+    <row r="33" ht="34" spans="1:6">
+      <c r="A33" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="E33" s="28" t="s">
+      <c r="E33" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="F33" s="28" t="s">
+      <c r="F33" s="33" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="45">
-      <c r="A34" s="4" t="s">
+    <row r="34" ht="51" spans="1:6">
+      <c r="A34" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B34" s="30" t="s">
+      <c r="B34" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="6" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="45">
-      <c r="A35" s="28" t="s">
+    <row r="35" ht="34" spans="1:6">
+      <c r="A35" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="28" t="s">
+      <c r="C35" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="D35" s="28" t="s">
+      <c r="D35" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="E35" s="28" t="s">
+      <c r="E35" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="F35" s="28" t="s">
+      <c r="F35" s="33" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="45">
-      <c r="A36" s="4" t="s">
+    <row r="36" ht="34" spans="1:6">
+      <c r="A36" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B36" s="30" t="s">
+      <c r="B36" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="6" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="45">
-      <c r="A37" s="28" t="s">
+    <row r="37" ht="34" spans="1:6">
+      <c r="A37" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="28" t="s">
+      <c r="C37" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="E37" s="28" t="s">
+      <c r="E37" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="F37" s="28" t="s">
+      <c r="F37" s="33" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="45">
-      <c r="A38" s="4" t="s">
+    <row r="38" ht="34" spans="1:6">
+      <c r="A38" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="6" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="45">
-      <c r="A39" s="28" t="s">
+    <row r="39" ht="34" spans="1:6">
+      <c r="A39" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="B39" s="29" t="s">
+      <c r="B39" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="28" t="s">
+      <c r="C39" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="28" t="s">
+      <c r="D39" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="E39" s="28" t="s">
+      <c r="E39" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="F39" s="28" t="s">
+      <c r="F39" s="33" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="45">
-      <c r="A40" s="4" t="s">
+    <row r="40" ht="51" spans="1:6">
+      <c r="A40" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B40" s="30" t="s">
+      <c r="B40" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="6" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="45">
-      <c r="A41" s="28" t="s">
+    <row r="41" ht="51" spans="1:6">
+      <c r="A41" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="B41" s="29" t="s">
+      <c r="B41" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="28" t="s">
+      <c r="C41" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="D41" s="28" t="s">
+      <c r="D41" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="E41" s="28" t="s">
+      <c r="E41" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="F41" s="28" t="s">
+      <c r="F41" s="33" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="30">
-      <c r="A42" s="4" t="s">
+    <row r="42" ht="34" spans="1:6">
+      <c r="A42" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B42" s="30" t="s">
+      <c r="B42" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="6" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="45">
-      <c r="A43" s="28" t="s">
+    <row r="43" ht="34" spans="1:6">
+      <c r="A43" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="C43" s="28" t="s">
+      <c r="C43" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="28" t="s">
+      <c r="D43" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="E43" s="28" t="s">
+      <c r="E43" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="F43" s="28" t="s">
+      <c r="F43" s="33" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="45">
-      <c r="A44" s="4" t="s">
+    <row r="44" ht="34" spans="1:6">
+      <c r="A44" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B44" s="30" t="s">
+      <c r="B44" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="6" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="45">
-      <c r="A45" s="28" t="s">
+    <row r="45" ht="34" spans="1:6">
+      <c r="A45" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="B45" s="29" t="s">
+      <c r="B45" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D45" s="28" t="s">
+      <c r="D45" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="E45" s="28" t="s">
+      <c r="E45" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="F45" s="28" t="s">
+      <c r="F45" s="33" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="45">
-      <c r="A46" s="4" t="s">
+    <row r="46" ht="51" spans="1:6">
+      <c r="A46" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B46" s="30" t="s">
+      <c r="B46" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="6" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="60">
-      <c r="A47" s="28" t="s">
+    <row r="47" ht="51" spans="1:6">
+      <c r="A47" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="C47" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="D47" s="28" t="s">
+      <c r="D47" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="E47" s="28" t="s">
+      <c r="E47" s="33" t="s">
         <v>206</v>
       </c>
-      <c r="F47" s="28" t="s">
+      <c r="F47" s="33" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="45">
-      <c r="A48" s="4" t="s">
+    <row r="48" ht="51" spans="1:6">
+      <c r="A48" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B48" s="30" t="s">
+      <c r="B48" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="6" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="45">
-      <c r="A49" s="28" t="s">
+    <row r="49" ht="34" spans="1:6">
+      <c r="A49" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="B49" s="29" t="s">
+      <c r="B49" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="C49" s="28" t="s">
+      <c r="C49" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="D49" s="28" t="s">
+      <c r="D49" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="E49" s="28" t="s">
+      <c r="E49" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="F49" s="28" t="s">
+      <c r="F49" s="33" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="45">
-      <c r="A50" s="4" t="s">
+    <row r="50" ht="34" spans="1:6">
+      <c r="A50" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="B50" s="30" t="s">
+      <c r="B50" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="6" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="45">
-      <c r="A51" s="28" t="s">
+    <row r="51" ht="51" spans="1:6">
+      <c r="A51" s="33" t="s">
         <v>220</v>
       </c>
-      <c r="B51" s="29" t="s">
+      <c r="B51" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="C51" s="28" t="s">
+      <c r="C51" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="D51" s="28" t="s">
+      <c r="D51" s="33" t="s">
         <v>221</v>
       </c>
-      <c r="E51" s="28" t="s">
+      <c r="E51" s="33" t="s">
         <v>222</v>
       </c>
-      <c r="F51" s="28" t="s">
+      <c r="F51" s="33" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="45">
-      <c r="A52" s="4" t="s">
+    <row r="52" ht="34" spans="1:6">
+      <c r="A52" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B52" s="30" t="s">
+      <c r="B52" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="6" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="45">
-      <c r="A53" s="28" t="s">
+    <row r="53" ht="34" spans="1:6">
+      <c r="A53" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="B53" s="29" t="s">
+      <c r="B53" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="C53" s="28" t="s">
+      <c r="C53" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="D53" s="28" t="s">
+      <c r="D53" s="33" t="s">
         <v>229</v>
       </c>
-      <c r="E53" s="28" t="s">
+      <c r="E53" s="33" t="s">
         <v>230</v>
       </c>
-      <c r="F53" s="28" t="s">
+      <c r="F53" s="33" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="45">
-      <c r="A54" s="4" t="s">
+    <row r="54" ht="34" spans="1:6">
+      <c r="A54" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="B54" s="30" t="s">
+      <c r="B54" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" s="6" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15">
-      <c r="A56" s="34" t="s">
+    <row r="56" spans="1:1">
+      <c r="A56" s="23" t="s">
         <v>236</v>
       </c>
-      <c r="B56" s="32"/>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="32"/>
-      <c r="F56" s="32"/>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="35" t="s">
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="24" t="s">
         <v>237</v>
       </c>
-      <c r="B57" s="32"/>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="35" t="s">
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B58" s="32"/>
-      <c r="C58" s="32"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="32"/>
-      <c r="F58" s="32"/>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="35" t="s">
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="B59" s="32"/>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="32"/>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="35" t="s">
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="24" t="s">
         <v>240</v>
       </c>
-      <c r="B60" s="32"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="32"/>
-      <c r="F60" s="32"/>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="35" t="s">
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="24" t="s">
         <v>241</v>
       </c>
-      <c r="B61" s="32"/>
-      <c r="C61" s="32"/>
-      <c r="D61" s="32"/>
-      <c r="E61" s="32"/>
-      <c r="F61" s="32"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="35" t="s">
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="B62" s="32"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="32"/>
-      <c r="E62" s="32"/>
-      <c r="F62" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="A62:F62"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A62:F62"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.8359375" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="55" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17">
-      <c r="A1" s="36" t="s">
+    <row r="1" ht="19.2" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-    </row>
-    <row r="2" spans="1:6" ht="15">
-      <c r="A2" s="33" t="s">
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-    </row>
-    <row r="4" spans="1:6" ht="15">
-      <c r="A4" s="1" t="s">
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="3" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="45">
-      <c r="A5" s="2" t="s">
+    <row r="5" ht="34" spans="1:6">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="45">
-      <c r="A6" s="4" t="s">
+    <row r="6" ht="34" spans="1:6">
+      <c r="A6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="6" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="45">
-      <c r="A7" s="2" t="s">
+    <row r="7" ht="51" spans="1:6">
+      <c r="A7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="29" t="s">
         <v>257</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="45">
-      <c r="A8" s="4" t="s">
+    <row r="8" ht="34" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="6" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="45">
-      <c r="A9" s="2" t="s">
+    <row r="9" ht="51" spans="1:6">
+      <c r="A9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="29" t="s">
         <v>266</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="4" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="45">
-      <c r="A10" s="4" t="s">
+    <row r="10" ht="51" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="30" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="6" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="45">
-      <c r="A11" s="2" t="s">
+    <row r="11" ht="34" spans="1:6">
+      <c r="A11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="29" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="30">
-      <c r="A12" s="4" t="s">
+    <row r="12" ht="34" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="6" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="45">
-      <c r="A13" s="2" t="s">
+    <row r="13" ht="51" spans="1:6">
+      <c r="A13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="4" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="45">
-      <c r="A14" s="4" t="s">
+    <row r="14" ht="34" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="6" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="45">
-      <c r="A15" s="2" t="s">
+    <row r="15" ht="34" spans="1:6">
+      <c r="A15" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="4" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="45">
-      <c r="A16" s="4" t="s">
+    <row r="16" ht="34" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="30" t="s">
         <v>296</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="6" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="45">
-      <c r="A17" s="2" t="s">
+    <row r="17" ht="34" spans="1:6">
+      <c r="A17" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="4" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="45">
-      <c r="A18" s="4" t="s">
+    <row r="18" ht="34" spans="1:6">
+      <c r="A18" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="45">
-      <c r="A19" s="2" t="s">
+    <row r="19" ht="34" spans="1:6">
+      <c r="A19" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="29" t="s">
         <v>310</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="4" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="30">
-      <c r="A20" s="4" t="s">
+    <row r="20" ht="34" spans="1:6">
+      <c r="A20" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="30" t="s">
         <v>310</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="6" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="45">
-      <c r="A21" s="2" t="s">
+    <row r="21" ht="34" spans="1:6">
+      <c r="A21" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="4" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="45">
-      <c r="A22" s="4" t="s">
+    <row r="22" ht="51" spans="1:6">
+      <c r="A22" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="6" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="45">
-      <c r="A23" s="2" t="s">
+    <row r="23" ht="34" spans="1:6">
+      <c r="A23" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="4" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="45">
-      <c r="A24" s="4" t="s">
+    <row r="24" ht="34" spans="1:6">
+      <c r="A24" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="6" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="45">
-      <c r="A25" s="2" t="s">
+    <row r="25" ht="34" spans="1:6">
+      <c r="A25" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="29" t="s">
         <v>331</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="4" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="45">
-      <c r="A26" s="4" t="s">
+    <row r="26" ht="34" spans="1:6">
+      <c r="A26" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="6" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="45">
-      <c r="A27" s="2" t="s">
+    <row r="27" ht="34" spans="1:6">
+      <c r="A27" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="4" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="45">
-      <c r="A28" s="4" t="s">
+    <row r="28" ht="34" spans="1:6">
+      <c r="A28" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="30" t="s">
         <v>341</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="6" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="45">
-      <c r="A29" s="2" t="s">
+    <row r="29" ht="34" spans="1:6">
+      <c r="A29" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="45">
-      <c r="A30" s="4" t="s">
+    <row r="30" ht="34" spans="1:6">
+      <c r="A30" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B30" s="26" t="s">
+      <c r="B30" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="6" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="45">
-      <c r="A31" s="2" t="s">
+    <row r="31" ht="34" spans="1:6">
+      <c r="A31" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="4" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="60">
-      <c r="A32" s="4" t="s">
+    <row r="32" ht="51" spans="1:6">
+      <c r="A32" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="6" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="45">
-      <c r="A33" s="2" t="s">
+    <row r="33" ht="34" spans="1:6">
+      <c r="A33" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="4" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="45">
-      <c r="A34" s="4" t="s">
+    <row r="34" ht="34" spans="1:6">
+      <c r="A34" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="6" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="45">
-      <c r="A35" s="2" t="s">
+    <row r="35" ht="51" spans="1:6">
+      <c r="A35" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="29" t="s">
         <v>310</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="4" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="45">
-      <c r="A36" s="4" t="s">
+    <row r="36" ht="51" spans="1:6">
+      <c r="A36" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B36" s="26" t="s">
+      <c r="B36" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="6" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="45">
-      <c r="A37" s="2" t="s">
+    <row r="37" ht="51" spans="1:6">
+      <c r="A37" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="29" t="s">
         <v>271</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="4" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="45">
-      <c r="A38" s="4" t="s">
+    <row r="38" ht="34" spans="1:6">
+      <c r="A38" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B38" s="26" t="s">
+      <c r="B38" s="30" t="s">
         <v>341</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="6" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="45">
-      <c r="A39" s="2" t="s">
+    <row r="39" ht="34" spans="1:6">
+      <c r="A39" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="4" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="45">
-      <c r="A40" s="4" t="s">
+    <row r="40" ht="34" spans="1:6">
+      <c r="A40" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B40" s="26" t="s">
+      <c r="B40" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="6" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="45">
-      <c r="A41" s="2" t="s">
+    <row r="41" ht="51" spans="1:6">
+      <c r="A41" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B41" s="25" t="s">
+      <c r="B41" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="4" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="45">
-      <c r="A42" s="4" t="s">
+    <row r="42" ht="34" spans="1:6">
+      <c r="A42" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B42" s="26" t="s">
+      <c r="B42" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="6" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="45">
-      <c r="A43" s="2" t="s">
+    <row r="43" ht="34" spans="1:6">
+      <c r="A43" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="29" t="s">
         <v>271</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="4" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="45">
-      <c r="A44" s="4" t="s">
+    <row r="44" ht="34" spans="1:6">
+      <c r="A44" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B44" s="26" t="s">
+      <c r="B44" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="6" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="30">
-      <c r="A45" s="2" t="s">
+    <row r="45" ht="34" spans="1:6">
+      <c r="A45" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B45" s="25" t="s">
+      <c r="B45" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="4" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="45">
-      <c r="A46" s="4" t="s">
+    <row r="46" ht="51" spans="1:6">
+      <c r="A46" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B46" s="26" t="s">
+      <c r="B46" s="30" t="s">
         <v>271</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="6" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="60">
-      <c r="A47" s="2" t="s">
+    <row r="47" ht="51" spans="1:6">
+      <c r="A47" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="B47" s="25" t="s">
+      <c r="B47" s="29" t="s">
         <v>271</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="4" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="45">
-      <c r="A48" s="4" t="s">
+    <row r="48" ht="51" spans="1:6">
+      <c r="A48" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B48" s="26" t="s">
+      <c r="B48" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="6" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="45">
-      <c r="A49" s="2" t="s">
+    <row r="49" ht="34" spans="1:6">
+      <c r="A49" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="4" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="45">
-      <c r="A50" s="4" t="s">
+    <row r="50" ht="51" spans="1:6">
+      <c r="A50" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="B50" s="26" t="s">
+      <c r="B50" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="6" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="45">
-      <c r="A51" s="2" t="s">
+    <row r="51" ht="34" spans="1:6">
+      <c r="A51" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B51" s="25" t="s">
+      <c r="B51" s="29" t="s">
         <v>331</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="4" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="45">
-      <c r="A52" s="4" t="s">
+    <row r="52" ht="51" spans="1:6">
+      <c r="A52" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B52" s="26" t="s">
+      <c r="B52" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="6" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="45">
-      <c r="A53" s="2" t="s">
+    <row r="53" ht="34" spans="1:6">
+      <c r="A53" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="B53" s="25" t="s">
+      <c r="B53" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" s="4" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="45">
-      <c r="A54" s="4" t="s">
+    <row r="54" ht="51" spans="1:6">
+      <c r="A54" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="B54" s="26" t="s">
+      <c r="B54" s="30" t="s">
         <v>341</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" s="6" t="s">
         <v>423</v>
       </c>
     </row>
@@ -4590,2131 +5083,2068 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="29.33203125" customWidth="1"/>
-    <col min="8" max="8" width="65.33203125" customWidth="1"/>
+    <col min="7" max="7" width="29.3359375" customWidth="1"/>
+    <col min="8" max="8" width="65.3359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17">
-      <c r="A1" s="36" t="s">
+    <row r="1" ht="19.2" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-    </row>
-    <row r="2" spans="1:8" ht="15">
-      <c r="A2" s="33" t="s">
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-    </row>
-    <row r="4" spans="1:8" ht="15">
-      <c r="A4" s="14" t="s">
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="16" t="s">
         <v>426</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>572</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>573</v>
-      </c>
-      <c r="E4" s="14" t="s">
+      <c r="C4" s="16" t="s">
         <v>427</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="D4" s="16" t="s">
         <v>428</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="E4" s="16" t="s">
         <v>429</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="F4" s="16" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="30">
-      <c r="A5" s="15">
+      <c r="G4" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="5" ht="34" spans="1:8">
+      <c r="A5" s="17">
         <v>1</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="19">
         <v>0.125</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="19">
         <v>0.08</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="25">
         <v>450</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="17">
         <f>4.5%</f>
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="G5" s="22" t="s">
+        <v>0.045</v>
+      </c>
+      <c r="G5" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="22" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="30">
-      <c r="A6" s="18">
+      <c r="H5" s="26" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="6" ht="34" spans="1:8">
+      <c r="A6" s="20">
         <v>2</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="22">
         <v>0.125</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="22">
         <v>0.08</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="25">
         <v>450</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="20">
         <f>4.5%</f>
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="G6" s="4" t="s">
+        <v>0.045</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="30">
-      <c r="A7" s="15">
+      <c r="H6" s="6" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="7" ht="34" spans="1:8">
+      <c r="A7" s="17">
         <v>3</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="19">
         <v>0.12</v>
       </c>
-      <c r="D7" s="17">
-        <v>7.7499999999999999E-2</v>
-      </c>
-      <c r="E7" s="21">
+      <c r="D7" s="19">
+        <v>0.0775</v>
+      </c>
+      <c r="E7" s="25">
         <v>425</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="17">
         <f>4.25%</f>
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="G7" s="22" t="s">
+        <v>0.0425</v>
+      </c>
+      <c r="G7" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="H7" s="22" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="30">
-      <c r="A8" s="18">
+      <c r="H7" s="26" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="8" ht="34" spans="1:8">
+      <c r="A8" s="20">
         <v>4</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="22">
         <v>0.12</v>
       </c>
-      <c r="D8" s="20">
-        <v>7.7499999999999999E-2</v>
-      </c>
-      <c r="E8" s="21">
+      <c r="D8" s="22">
+        <v>0.0775</v>
+      </c>
+      <c r="E8" s="25">
         <v>425</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="20">
         <f>4.25%</f>
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="G8" s="4" t="s">
+        <v>0.0425</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="30">
-      <c r="A9" s="15">
+      <c r="H8" s="6" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="9" ht="34" spans="1:8">
+      <c r="A9" s="17">
         <v>5</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="19">
         <v>0.11</v>
       </c>
-      <c r="D9" s="17">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E9" s="21">
+      <c r="D9" s="19">
+        <v>0.07</v>
+      </c>
+      <c r="E9" s="25">
         <v>400</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="17">
         <f t="shared" ref="F9:F24" si="0">4%</f>
         <v>0.04</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="22" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="30">
-      <c r="A10" s="18">
+      <c r="H9" s="26" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="10" ht="34" spans="1:8">
+      <c r="A10" s="20">
         <v>6</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="22">
         <v>0.115</v>
       </c>
-      <c r="D10" s="20">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="E10" s="21">
+      <c r="D10" s="22">
+        <v>0.075</v>
+      </c>
+      <c r="E10" s="25">
         <v>400</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="20">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="16">
-      <c r="A11" s="15">
+      <c r="H10" s="6" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" ht="17.6" spans="1:8">
+      <c r="A11" s="17">
         <v>7</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="17">
-        <v>0.10249999999999999</v>
-      </c>
-      <c r="D11" s="17">
-        <v>6.25E-2</v>
-      </c>
-      <c r="E11" s="21">
+      <c r="C11" s="19">
+        <v>0.1025</v>
+      </c>
+      <c r="D11" s="19">
+        <v>0.0625</v>
+      </c>
+      <c r="E11" s="25">
         <v>400</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="17">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="22" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="30">
-      <c r="A12" s="18">
+      <c r="H11" s="26" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="12" ht="34" spans="1:8">
+      <c r="A12" s="20">
         <v>8</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="20">
-        <v>0.10249999999999999</v>
-      </c>
-      <c r="D12" s="20">
-        <v>6.25E-2</v>
-      </c>
-      <c r="E12" s="21">
+      <c r="C12" s="22">
+        <v>0.1025</v>
+      </c>
+      <c r="D12" s="22">
+        <v>0.0625</v>
+      </c>
+      <c r="E12" s="25">
         <v>400</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="20">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="16">
-      <c r="A13" s="15">
+      <c r="G12" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="13" ht="17.6" spans="1:8">
+      <c r="A13" s="17">
         <v>9</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="19">
         <v>0.105</v>
       </c>
-      <c r="D13" s="17">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="E13" s="21">
+      <c r="D13" s="19">
+        <v>0.065</v>
+      </c>
+      <c r="E13" s="25">
         <v>400</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="17">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="H13" s="22" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="16">
-      <c r="A14" s="18">
+      <c r="H13" s="26" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="14" ht="17.6" spans="1:8">
+      <c r="A14" s="20">
         <v>10</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="22">
         <v>0.1125</v>
       </c>
-      <c r="D14" s="20">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="E14" s="21">
+      <c r="D14" s="22">
+        <v>0.0725</v>
+      </c>
+      <c r="E14" s="25">
         <v>400</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="20">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="16">
-      <c r="A15" s="15">
+      <c r="H14" s="6" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="15" ht="17.6" spans="1:8">
+      <c r="A15" s="17">
         <v>11</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="19">
         <v>0.1125</v>
       </c>
-      <c r="D15" s="17">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="E15" s="21">
+      <c r="D15" s="19">
+        <v>0.0725</v>
+      </c>
+      <c r="E15" s="25">
         <v>400</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="17">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="H15" s="22" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="30">
-      <c r="A16" s="18">
+      <c r="H15" s="26" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="16" ht="17.6" spans="1:8">
+      <c r="A16" s="20">
         <v>12</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="22">
         <v>0.1075</v>
       </c>
-      <c r="D16" s="20">
-        <v>6.7500000000000004E-2</v>
-      </c>
-      <c r="E16" s="21">
+      <c r="D16" s="22">
+        <v>0.0675</v>
+      </c>
+      <c r="E16" s="25">
         <v>400</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="20">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="16">
-      <c r="A17" s="15">
+      <c r="H16" s="6" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="17" ht="17.6" spans="1:8">
+      <c r="A17" s="17">
         <v>13</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="19">
         <v>0.11</v>
       </c>
-      <c r="D17" s="17">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E17" s="21">
+      <c r="D17" s="19">
+        <v>0.07</v>
+      </c>
+      <c r="E17" s="25">
         <v>400</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="17">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="H17" s="22" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="30">
-      <c r="A18" s="18">
+      <c r="H17" s="26" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="18" ht="17.6" spans="1:8">
+      <c r="A18" s="20">
         <v>14</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="22">
         <v>0.1125</v>
       </c>
-      <c r="D18" s="20">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="E18" s="21">
+      <c r="D18" s="22">
+        <v>0.0725</v>
+      </c>
+      <c r="E18" s="25">
         <v>400</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="20">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="30">
-      <c r="A19" s="15">
+      <c r="H18" s="6" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="19" ht="34" spans="1:8">
+      <c r="A19" s="17">
         <v>15</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="19">
         <v>0.1</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="19">
         <v>0.06</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="25">
         <v>400</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="17">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G19" s="22" t="s">
-        <v>446</v>
-      </c>
-      <c r="H19" s="22" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="16">
-      <c r="A20" s="18">
+      <c r="G19" s="26" t="s">
+        <v>448</v>
+      </c>
+      <c r="H19" s="26" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="20" ht="17.6" spans="1:8">
+      <c r="A20" s="20">
         <v>16</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="22">
         <v>0.115</v>
       </c>
-      <c r="D20" s="20">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="E20" s="21">
+      <c r="D20" s="22">
+        <v>0.075</v>
+      </c>
+      <c r="E20" s="25">
         <v>400</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="20">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="30">
-      <c r="A21" s="15">
+      <c r="H20" s="6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="21" ht="34" spans="1:8">
+      <c r="A21" s="17">
         <v>17</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="C21" s="17">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="D21" s="17">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="E21" s="21">
+      <c r="C21" s="19">
+        <v>0.0975</v>
+      </c>
+      <c r="D21" s="19">
+        <v>0.0575</v>
+      </c>
+      <c r="E21" s="25">
         <v>400</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="17">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G21" s="22" t="s">
-        <v>449</v>
-      </c>
-      <c r="H21" s="22" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="30">
-      <c r="A22" s="18">
+      <c r="G21" s="26" t="s">
+        <v>451</v>
+      </c>
+      <c r="H21" s="26" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="22" ht="34" spans="1:8">
+      <c r="A22" s="20">
         <v>18</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="C22" s="20">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="D22" s="20">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="E22" s="21">
+      <c r="C22" s="22">
+        <v>0.0975</v>
+      </c>
+      <c r="D22" s="22">
+        <v>0.0575</v>
+      </c>
+      <c r="E22" s="25">
         <v>400</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="20">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="16">
-      <c r="A23" s="15">
+      <c r="G22" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="23" ht="17.6" spans="1:8">
+      <c r="A23" s="17">
         <v>19</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="19">
         <v>0.1075</v>
       </c>
-      <c r="D23" s="17">
-        <v>6.7500000000000004E-2</v>
-      </c>
-      <c r="E23" s="21">
+      <c r="D23" s="19">
+        <v>0.0675</v>
+      </c>
+      <c r="E23" s="25">
         <v>400</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="17">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G23" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="H23" s="22" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="16">
-      <c r="A24" s="18">
+      <c r="H23" s="26" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="24" ht="17.6" spans="1:8">
+      <c r="A24" s="20">
         <v>20</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="22">
         <v>0.12</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="22">
         <v>0.08</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="25">
         <v>400</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="20">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="30">
-      <c r="A25" s="15">
+      <c r="H24" s="6" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="25" ht="34" spans="1:8">
+      <c r="A25" s="17">
         <v>21</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="17">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="D25" s="17">
+      <c r="C25" s="19">
+        <v>0.0975</v>
+      </c>
+      <c r="D25" s="19">
         <v>0.06</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="25">
         <v>375</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="17">
         <f t="shared" ref="F25:F48" si="1">3.75%</f>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>455</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="30">
-      <c r="A26" s="18">
+        <v>0.0375</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>457</v>
+      </c>
+      <c r="H25" s="26" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="26" ht="17.6" spans="1:8">
+      <c r="A26" s="20">
         <v>22</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="22">
         <v>0.1</v>
       </c>
-      <c r="D26" s="20">
-        <v>6.25E-2</v>
-      </c>
-      <c r="E26" s="21">
+      <c r="D26" s="22">
+        <v>0.0625</v>
+      </c>
+      <c r="E26" s="25">
         <v>375</v>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="20">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G26" s="4" t="s">
+        <v>0.0375</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="30">
-      <c r="A27" s="15">
+      <c r="H26" s="6" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="27" ht="34" spans="1:8">
+      <c r="A27" s="17">
         <v>23</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="19">
         <v>0.105</v>
       </c>
-      <c r="D27" s="17">
-        <v>6.7500000000000004E-2</v>
-      </c>
-      <c r="E27" s="21">
+      <c r="D27" s="19">
+        <v>0.0675</v>
+      </c>
+      <c r="E27" s="25">
         <v>375</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="17">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G27" s="22" t="s">
-        <v>458</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="30">
-      <c r="A28" s="18">
+        <v>0.0375</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>460</v>
+      </c>
+      <c r="H27" s="26" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="28" ht="34" spans="1:8">
+      <c r="A28" s="20">
         <v>24</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="20">
+      <c r="C28" s="22">
         <v>0.1075</v>
       </c>
-      <c r="D28" s="20">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E28" s="21">
+      <c r="D28" s="22">
+        <v>0.07</v>
+      </c>
+      <c r="E28" s="25">
         <v>375</v>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="20">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="16">
-      <c r="A29" s="15">
+        <v>0.0375</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="29" ht="17.6" spans="1:8">
+      <c r="A29" s="17">
         <v>25</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="19">
         <v>0.1075</v>
       </c>
-      <c r="D29" s="17">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E29" s="21">
+      <c r="D29" s="19">
+        <v>0.07</v>
+      </c>
+      <c r="E29" s="25">
         <v>375</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="17">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G29" s="22" t="s">
+        <v>0.0375</v>
+      </c>
+      <c r="G29" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="H29" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="30">
-      <c r="A30" s="18">
+      <c r="H29" s="26" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="30" ht="34" spans="1:8">
+      <c r="A30" s="20">
         <v>26</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="20">
+      <c r="C30" s="22">
         <v>0.11</v>
       </c>
-      <c r="D30" s="20">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="E30" s="21">
+      <c r="D30" s="22">
+        <v>0.0725</v>
+      </c>
+      <c r="E30" s="25">
         <v>375</v>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="20">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="30">
-      <c r="A31" s="15">
+        <v>0.0375</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="31" ht="17.6" spans="1:8">
+      <c r="A31" s="17">
         <v>27</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="19">
         <v>0.1075</v>
       </c>
-      <c r="D31" s="17">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E31" s="21">
+      <c r="D31" s="19">
+        <v>0.07</v>
+      </c>
+      <c r="E31" s="25">
         <v>375</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="17">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G31" s="22" t="s">
+        <v>0.0375</v>
+      </c>
+      <c r="G31" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="H31" s="22" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="30">
-      <c r="A32" s="18">
+      <c r="H31" s="26" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="32" ht="34" spans="1:8">
+      <c r="A32" s="20">
         <v>28</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="C32" s="20">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="D32" s="20">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="E32" s="21">
+      <c r="C32" s="22">
+        <v>0.095</v>
+      </c>
+      <c r="D32" s="22">
+        <v>0.0575</v>
+      </c>
+      <c r="E32" s="25">
         <v>375</v>
       </c>
-      <c r="F32" s="18">
+      <c r="F32" s="20">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="30">
-      <c r="A33" s="15">
+        <v>0.0375</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="33" ht="34" spans="1:8">
+      <c r="A33" s="17">
         <v>29</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="17">
-        <v>9.2499999999999999E-2</v>
-      </c>
-      <c r="D33" s="17">
-        <v>5.5E-2</v>
-      </c>
-      <c r="E33" s="21">
+      <c r="C33" s="19">
+        <v>0.0925</v>
+      </c>
+      <c r="D33" s="19">
+        <v>0.055</v>
+      </c>
+      <c r="E33" s="25">
         <v>375</v>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="17">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G33" s="22" t="s">
+        <v>0.0375</v>
+      </c>
+      <c r="G33" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="H33" s="22" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="30">
-      <c r="A34" s="18">
+      <c r="H33" s="26" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="34" ht="34" spans="1:8">
+      <c r="A34" s="20">
         <v>30</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="22">
         <v>0.11</v>
       </c>
-      <c r="D34" s="20">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="E34" s="21">
+      <c r="D34" s="22">
+        <v>0.0725</v>
+      </c>
+      <c r="E34" s="25">
         <v>375</v>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="20">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="30">
-      <c r="A35" s="15">
+        <v>0.0375</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="35" ht="17.6" spans="1:8">
+      <c r="A35" s="17">
         <v>31</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C35" s="17">
+      <c r="C35" s="19">
         <v>0.105</v>
       </c>
-      <c r="D35" s="17">
-        <v>6.7500000000000004E-2</v>
-      </c>
-      <c r="E35" s="21">
+      <c r="D35" s="19">
+        <v>0.0675</v>
+      </c>
+      <c r="E35" s="25">
         <v>375</v>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G35" s="22" t="s">
+        <v>0.0375</v>
+      </c>
+      <c r="G35" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="H35" s="22" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="16">
-      <c r="A36" s="18">
+      <c r="H35" s="26" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="36" ht="17.6" spans="1:8">
+      <c r="A36" s="20">
         <v>32</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="22">
         <v>0.11</v>
       </c>
-      <c r="D36" s="20">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="E36" s="21">
+      <c r="D36" s="22">
+        <v>0.0725</v>
+      </c>
+      <c r="E36" s="25">
         <v>375</v>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="20">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G36" s="4" t="s">
+        <v>0.0375</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="H36" s="4" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="30">
-      <c r="A37" s="15">
+      <c r="H36" s="6" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="37" ht="34" spans="1:8">
+      <c r="A37" s="17">
         <v>33</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="C37" s="17">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="D37" s="17">
+      <c r="C37" s="19">
+        <v>0.0975</v>
+      </c>
+      <c r="D37" s="19">
         <v>0.06</v>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="25">
         <v>375</v>
       </c>
-      <c r="F37" s="15">
+      <c r="F37" s="17">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G37" s="22" t="s">
-        <v>473</v>
-      </c>
-      <c r="H37" s="22" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="16">
-      <c r="A38" s="18">
+        <v>0.0375</v>
+      </c>
+      <c r="G37" s="26" t="s">
+        <v>475</v>
+      </c>
+      <c r="H37" s="26" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="38" ht="17.6" spans="1:8">
+      <c r="A38" s="20">
         <v>34</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="C38" s="20">
+      <c r="C38" s="22">
         <v>0.105</v>
       </c>
-      <c r="D38" s="20">
-        <v>6.7500000000000004E-2</v>
-      </c>
-      <c r="E38" s="21">
+      <c r="D38" s="22">
+        <v>0.0675</v>
+      </c>
+      <c r="E38" s="25">
         <v>375</v>
       </c>
-      <c r="F38" s="18">
+      <c r="F38" s="20">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G38" s="4" t="s">
+        <v>0.0375</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="H38" s="4" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="30">
-      <c r="A39" s="15">
+      <c r="H38" s="6" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="39" ht="34" spans="1:8">
+      <c r="A39" s="17">
         <v>35</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="C39" s="17">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="D39" s="17">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="E39" s="21">
+      <c r="C39" s="19">
+        <v>0.095</v>
+      </c>
+      <c r="D39" s="19">
+        <v>0.0575</v>
+      </c>
+      <c r="E39" s="25">
         <v>375</v>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="17">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G39" s="22" t="s">
-        <v>476</v>
-      </c>
-      <c r="H39" s="22" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="30">
-      <c r="A40" s="18">
+        <v>0.0375</v>
+      </c>
+      <c r="G39" s="26" t="s">
+        <v>478</v>
+      </c>
+      <c r="H39" s="26" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="40" ht="34" spans="1:8">
+      <c r="A40" s="20">
         <v>36</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="22">
         <v>0.1075</v>
       </c>
-      <c r="D40" s="20">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E40" s="21">
+      <c r="D40" s="22">
+        <v>0.07</v>
+      </c>
+      <c r="E40" s="25">
         <v>375</v>
       </c>
-      <c r="F40" s="18">
+      <c r="F40" s="20">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="30">
-      <c r="A41" s="15">
+        <v>0.0375</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="41" ht="17.6" spans="1:8">
+      <c r="A41" s="17">
         <v>37</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="C41" s="17">
+      <c r="C41" s="19">
         <v>0.11</v>
       </c>
-      <c r="D41" s="17">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="E41" s="21">
+      <c r="D41" s="19">
+        <v>0.0725</v>
+      </c>
+      <c r="E41" s="25">
         <v>375</v>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="17">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G41" s="22" t="s">
+        <v>0.0375</v>
+      </c>
+      <c r="G41" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="H41" s="22" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="30">
-      <c r="A42" s="18">
+      <c r="H41" s="26" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="42" ht="34" spans="1:8">
+      <c r="A42" s="20">
         <v>38</v>
       </c>
-      <c r="B42" s="19" t="s">
+      <c r="B42" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="C42" s="20">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="D42" s="20">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="E42" s="21">
+      <c r="C42" s="22">
+        <v>0.095</v>
+      </c>
+      <c r="D42" s="22">
+        <v>0.0575</v>
+      </c>
+      <c r="E42" s="25">
         <v>375</v>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="20">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="30">
-      <c r="A43" s="15">
+        <v>0.0375</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="43" ht="17.6" spans="1:8">
+      <c r="A43" s="17">
         <v>39</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="C43" s="17">
-        <v>0.10249999999999999</v>
-      </c>
-      <c r="D43" s="17">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="E43" s="21">
+      <c r="C43" s="19">
+        <v>0.1025</v>
+      </c>
+      <c r="D43" s="19">
+        <v>0.065</v>
+      </c>
+      <c r="E43" s="25">
         <v>375</v>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="17">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G43" s="22" t="s">
-        <v>483</v>
-      </c>
-      <c r="H43" s="22" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="16">
-      <c r="A44" s="18">
+        <v>0.0375</v>
+      </c>
+      <c r="G43" s="26" t="s">
+        <v>485</v>
+      </c>
+      <c r="H43" s="26" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="44" ht="17.6" spans="1:8">
+      <c r="A44" s="20">
         <v>40</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="C44" s="20">
+      <c r="C44" s="22">
         <v>0.1</v>
       </c>
-      <c r="D44" s="20">
-        <v>6.25E-2</v>
-      </c>
-      <c r="E44" s="21">
+      <c r="D44" s="22">
+        <v>0.0625</v>
+      </c>
+      <c r="E44" s="25">
         <v>375</v>
       </c>
-      <c r="F44" s="18">
+      <c r="F44" s="20">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G44" s="4" t="s">
+        <v>0.0375</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="H44" s="4" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="30">
-      <c r="A45" s="15">
+      <c r="H44" s="6" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="45" ht="34" spans="1:8">
+      <c r="A45" s="17">
         <v>41</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="C45" s="17">
-        <v>0.10249999999999999</v>
-      </c>
-      <c r="D45" s="17">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="E45" s="21">
+      <c r="C45" s="19">
+        <v>0.1025</v>
+      </c>
+      <c r="D45" s="19">
+        <v>0.065</v>
+      </c>
+      <c r="E45" s="25">
         <v>375</v>
       </c>
-      <c r="F45" s="15">
+      <c r="F45" s="17">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G45" s="22" t="s">
-        <v>486</v>
-      </c>
-      <c r="H45" s="22" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="30">
-      <c r="A46" s="18">
+        <v>0.0375</v>
+      </c>
+      <c r="G45" s="26" t="s">
+        <v>488</v>
+      </c>
+      <c r="H45" s="26" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="46" ht="17.6" spans="1:8">
+      <c r="A46" s="20">
         <v>42</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="C46" s="20">
+      <c r="C46" s="22">
         <v>0.1</v>
       </c>
-      <c r="D46" s="20">
-        <v>6.25E-2</v>
-      </c>
-      <c r="E46" s="21">
+      <c r="D46" s="22">
+        <v>0.0625</v>
+      </c>
+      <c r="E46" s="25">
         <v>375</v>
       </c>
-      <c r="F46" s="18">
+      <c r="F46" s="20">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="16">
-      <c r="A47" s="15">
+        <v>0.0375</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="47" ht="17.6" spans="1:8">
+      <c r="A47" s="17">
         <v>43</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="C47" s="17">
+      <c r="C47" s="19">
         <v>0.11</v>
       </c>
-      <c r="D47" s="17">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="E47" s="21">
+      <c r="D47" s="19">
+        <v>0.0725</v>
+      </c>
+      <c r="E47" s="25">
         <v>375</v>
       </c>
-      <c r="F47" s="15">
+      <c r="F47" s="17">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G47" s="22" t="s">
+        <v>0.0375</v>
+      </c>
+      <c r="G47" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="H47" s="22" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="30">
-      <c r="A48" s="18">
+      <c r="H47" s="26" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="48" ht="34" spans="1:8">
+      <c r="A48" s="20">
         <v>44</v>
       </c>
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="21" t="s">
         <v>220</v>
       </c>
-      <c r="C48" s="20">
-        <v>9.2499999999999999E-2</v>
-      </c>
-      <c r="D48" s="20">
-        <v>5.5E-2</v>
-      </c>
-      <c r="E48" s="21">
+      <c r="C48" s="22">
+        <v>0.0925</v>
+      </c>
+      <c r="D48" s="22">
+        <v>0.055</v>
+      </c>
+      <c r="E48" s="25">
         <v>375</v>
       </c>
-      <c r="F48" s="18">
+      <c r="F48" s="20">
         <f t="shared" si="1"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="30">
-      <c r="A49" s="15">
+        <v>0.0375</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="49" ht="34" spans="1:8">
+      <c r="A49" s="17">
         <v>45</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C49" s="17">
+      <c r="C49" s="19">
         <v>0.09</v>
       </c>
-      <c r="D49" s="17">
-        <v>5.5E-2</v>
-      </c>
-      <c r="E49" s="23">
+      <c r="D49" s="19">
+        <v>0.055</v>
+      </c>
+      <c r="E49" s="27">
         <v>350</v>
       </c>
-      <c r="F49" s="15">
+      <c r="F49" s="17">
         <f>3.5%</f>
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="G49" s="22" t="s">
-        <v>493</v>
-      </c>
-      <c r="H49" s="22" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="30">
-      <c r="A50" s="18">
+        <v>0.035</v>
+      </c>
+      <c r="G49" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="H49" s="26" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="50" ht="34" spans="1:8">
+      <c r="A50" s="20">
         <v>46</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C50" s="20">
+      <c r="C50" s="22">
         <v>0.1</v>
       </c>
-      <c r="D50" s="20">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="E50" s="23">
+      <c r="D50" s="22">
+        <v>0.065</v>
+      </c>
+      <c r="E50" s="27">
         <v>350</v>
       </c>
-      <c r="F50" s="18">
+      <c r="F50" s="20">
         <f>3.5%</f>
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="30">
-      <c r="A51" s="15">
+        <v>0.035</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="51" ht="34" spans="1:8">
+      <c r="A51" s="17">
         <v>47</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="C51" s="17">
+      <c r="C51" s="19">
         <v>0.1</v>
       </c>
-      <c r="D51" s="17">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="E51" s="23">
+      <c r="D51" s="19">
+        <v>0.065</v>
+      </c>
+      <c r="E51" s="27">
         <v>350</v>
       </c>
-      <c r="F51" s="15">
+      <c r="F51" s="17">
         <f>3.5%</f>
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="G51" s="22" t="s">
-        <v>497</v>
-      </c>
-      <c r="H51" s="22" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="30">
-      <c r="A52" s="18">
+        <v>0.035</v>
+      </c>
+      <c r="G51" s="26" t="s">
+        <v>499</v>
+      </c>
+      <c r="H51" s="26" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="52" ht="34" spans="1:8">
+      <c r="A52" s="20">
         <v>48</v>
       </c>
-      <c r="B52" s="19" t="s">
+      <c r="B52" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C52" s="20">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="D52" s="20">
-        <v>6.25E-2</v>
-      </c>
-      <c r="E52" s="23">
+      <c r="C52" s="22">
+        <v>0.095</v>
+      </c>
+      <c r="D52" s="22">
+        <v>0.0625</v>
+      </c>
+      <c r="E52" s="27">
         <v>325</v>
       </c>
-      <c r="F52" s="18">
+      <c r="F52" s="20">
         <f>3.25%</f>
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="30">
-      <c r="A53" s="15">
+        <v>0.0325</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="53" ht="34" spans="1:8">
+      <c r="A53" s="17">
         <v>49</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="C53" s="17">
+      <c r="C53" s="19">
         <v>0.09</v>
       </c>
-      <c r="D53" s="17">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="E53" s="23">
+      <c r="D53" s="19">
+        <v>0.0575</v>
+      </c>
+      <c r="E53" s="27">
         <v>325</v>
       </c>
-      <c r="F53" s="15">
+      <c r="F53" s="17">
         <f>3.25%</f>
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="G53" s="22" t="s">
-        <v>501</v>
-      </c>
-      <c r="H53" s="22" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="30">
-      <c r="A54" s="18">
+        <v>0.0325</v>
+      </c>
+      <c r="G53" s="26" t="s">
+        <v>503</v>
+      </c>
+      <c r="H53" s="26" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="54" ht="34" spans="1:8">
+      <c r="A54" s="20">
         <v>50</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C54" s="20">
+      <c r="C54" s="22">
         <v>0.08</v>
       </c>
-      <c r="D54" s="20">
+      <c r="D54" s="22">
         <v>0.05</v>
       </c>
-      <c r="E54" s="24">
+      <c r="E54" s="28">
         <v>300</v>
       </c>
-      <c r="F54" s="18">
+      <c r="F54" s="20">
         <f>3%</f>
         <v>0.03</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G54" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="H54" s="4" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="15">
-      <c r="A56" s="34" t="s">
-        <v>504</v>
-      </c>
-      <c r="B56" s="32"/>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="32"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="35" t="s">
+      <c r="H54" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="B57" s="32"/>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32"/>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="35" t="s">
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="23" t="s">
         <v>506</v>
       </c>
-      <c r="B58" s="32"/>
-      <c r="C58" s="32"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="32"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="32"/>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="35" t="s">
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="24" t="s">
         <v>507</v>
       </c>
-      <c r="B59" s="32"/>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="35" t="s">
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="24" t="s">
         <v>508</v>
       </c>
-      <c r="B60" s="32"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="32"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="32"/>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="35" t="s">
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="24" t="s">
         <v>509</v>
       </c>
-      <c r="B61" s="32"/>
-      <c r="C61" s="32"/>
-      <c r="D61" s="32"/>
-      <c r="E61" s="32"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="32"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="35" t="s">
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="24" t="s">
         <v>510</v>
       </c>
-      <c r="B62" s="32"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="32"/>
-      <c r="E62" s="32"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="32"/>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="24" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="24" t="s">
+        <v>512</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A62:H62"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A56:H56"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A62:H62"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24.3359375" customWidth="1"/>
     <col min="2" max="2" width="75" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17">
-      <c r="A1" s="36"/>
-      <c r="B1" s="32"/>
-    </row>
-    <row r="2" spans="1:5" ht="15">
-      <c r="A2" s="33"/>
-      <c r="B2" s="32"/>
-    </row>
-    <row r="4" spans="1:5" ht="15">
-      <c r="A4" s="1" t="s">
+    <row r="1" ht="19.2" spans="1:1">
+      <c r="A1" s="1"/>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="E4" t="str" cm="1">
+      <c r="B4" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="E4" t="str">
         <f t="array" ref="E4:E12">_xlfn._xlws.SORT(_xlfn.UNIQUE(C5:C54))</f>
         <v>A</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="39">
-      <c r="A5" s="2" t="s">
+    <row r="5" ht="41" spans="1:5">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>514</v>
+      <c r="B5" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>516</v>
       </c>
       <c r="E5" t="str">
         <v>A+</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="26">
-      <c r="A6" s="4" t="s">
+    <row r="6" ht="41" spans="1:5">
+      <c r="A6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>516</v>
+      <c r="B6" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>518</v>
       </c>
       <c r="E6" t="str">
         <v>B</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="39">
-      <c r="A7" s="2" t="s">
+    <row r="7" ht="41" spans="1:5">
+      <c r="A7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>514</v>
+      <c r="B7" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>516</v>
       </c>
       <c r="E7" t="str">
         <v>B+</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="26">
-      <c r="A8" s="4" t="s">
+    <row r="8" ht="28" spans="1:5">
+      <c r="A8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>518</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>514</v>
+      <c r="B8" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>516</v>
       </c>
       <c r="E8" t="str">
         <v>C</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="39">
-      <c r="A9" s="2" t="s">
+    <row r="9" ht="55" spans="1:5">
+      <c r="A9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>520</v>
+      <c r="B9" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>522</v>
       </c>
       <c r="E9" t="str">
         <v>C-</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="39">
-      <c r="A10" s="4" t="s">
+    <row r="10" ht="41" spans="1:5">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>522</v>
+      <c r="B10" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>524</v>
       </c>
       <c r="E10" t="str">
         <v>D</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="39">
-      <c r="A11" s="2" t="s">
+    <row r="11" ht="41" spans="1:5">
+      <c r="A11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>524</v>
+      <c r="B11" s="11" t="s">
+        <v>525</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>526</v>
       </c>
       <c r="E11" t="str">
         <v>D-</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="26">
-      <c r="A12" s="4" t="s">
+    <row r="12" ht="28" spans="1:5">
+      <c r="A12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>525</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>522</v>
+      <c r="B12" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>524</v>
       </c>
       <c r="E12" t="str">
         <v>F</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="39">
-      <c r="A13" s="2" t="s">
+    <row r="13" ht="41" spans="1:3">
+      <c r="A13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="14" ht="41" spans="1:3">
+      <c r="A14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="15" ht="41" spans="1:3">
+      <c r="A15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>526</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="39">
-      <c r="A14" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="39">
-      <c r="A15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="C15" s="9" t="s">
+    </row>
+    <row r="16" ht="28" spans="1:3">
+      <c r="A16" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="17" ht="41" spans="1:3">
+      <c r="A17" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="18" ht="41" spans="1:3">
+      <c r="A18" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="19" ht="28" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="20" ht="28" spans="1:3">
+      <c r="A20" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="21" ht="28" spans="1:3">
+      <c r="A21" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>538</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="22" ht="41" spans="1:3">
+      <c r="A22" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="26">
-      <c r="A16" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>529</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="39">
-      <c r="A17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="26">
-      <c r="A18" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>532</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="26">
-      <c r="A19" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B19" s="11" t="s">
+    <row r="23" ht="41" spans="1:3">
+      <c r="A23" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="24" ht="41" spans="1:3">
+      <c r="A24" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="26">
-      <c r="A20" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="26">
-      <c r="A21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B21" s="11" t="s">
+    </row>
+    <row r="25" ht="55" spans="1:3">
+      <c r="A25" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="26" ht="41" spans="1:3">
+      <c r="A26" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="27" ht="41" spans="1:3">
+      <c r="A27" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="28" ht="28" spans="1:3">
+      <c r="A28" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="29" ht="41" spans="1:3">
+      <c r="A29" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>546</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>536</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="39">
-      <c r="A22" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>537</v>
-      </c>
-      <c r="C22" s="8" t="s">
+    </row>
+    <row r="30" ht="28" spans="1:3">
+      <c r="A30" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="31" ht="28" spans="1:3">
+      <c r="A31" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="32" ht="41" spans="1:3">
+      <c r="A32" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="33" ht="28" spans="1:3">
+      <c r="A33" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>550</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="34" ht="41" spans="1:3">
+      <c r="A34" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>551</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="35" ht="28" spans="1:3">
+      <c r="A35" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="36" ht="68" spans="1:3">
+      <c r="A36" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>553</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="26">
-      <c r="A23" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>538</v>
-      </c>
-      <c r="C23" s="10" t="s">
+    <row r="37" ht="41" spans="1:3">
+      <c r="A37" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="39">
-      <c r="A24" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="39">
-      <c r="A25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="39">
-      <c r="A26" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="39">
-      <c r="A27" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="C27" s="9" t="s">
+    <row r="38" ht="28" spans="1:3">
+      <c r="A38" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="39" ht="41" spans="1:3">
+      <c r="A39" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>556</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="40" ht="28" spans="1:3">
+      <c r="A40" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="41" ht="41" spans="1:3">
+      <c r="A41" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="42" ht="41" spans="1:3">
+      <c r="A42" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="26">
-      <c r="A28" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="26">
-      <c r="A29" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>544</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="26">
-      <c r="A30" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>545</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="26">
-      <c r="A31" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>546</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="39">
-      <c r="A32" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="26">
-      <c r="A33" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>548</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="39">
-      <c r="A34" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>549</v>
-      </c>
-      <c r="C34" s="12" t="s">
+    <row r="43" ht="41" spans="1:3">
+      <c r="A43" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="44" ht="41" spans="1:3">
+      <c r="A44" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="45" ht="28" spans="1:3">
+      <c r="A45" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="46" ht="41" spans="1:3">
+      <c r="A46" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="47" ht="55" spans="1:3">
+      <c r="A47" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="48" ht="28" spans="1:3">
+      <c r="A48" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="49" ht="41" spans="1:3">
+      <c r="A49" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="50" ht="41" spans="1:3">
+      <c r="A50" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="C50" s="10" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="26">
-      <c r="A35" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>550</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="52">
-      <c r="A36" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>551</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="39">
-      <c r="A37" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="26">
-      <c r="A38" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="39">
-      <c r="A39" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>554</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="26">
-      <c r="A40" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="39">
-      <c r="A41" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="39">
-      <c r="A42" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>558</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="39">
-      <c r="A43" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>559</v>
-      </c>
-      <c r="C43" s="10" t="s">
+    <row r="51" ht="41" spans="1:3">
+      <c r="A51" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="52" ht="41" spans="1:3">
+      <c r="A52" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="53" ht="28" spans="1:3">
+      <c r="A53" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="54" ht="28" spans="1:3">
+      <c r="A54" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="C54" s="8" t="s">
         <v>516</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="39">
-      <c r="A44" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>560</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="26">
-      <c r="A45" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="39">
-      <c r="A46" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>562</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="52">
-      <c r="A47" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="26">
-      <c r="A48" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>565</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="39">
-      <c r="A49" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>566</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="39">
-      <c r="A50" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>567</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="39">
-      <c r="A51" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="26">
-      <c r="A52" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="26">
-      <c r="A53" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>570</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="26">
-      <c r="A54" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -6722,7 +7152,7 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>